--- a/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="E2">
-        <v>0.15</v>
+        <v>0.081</v>
       </c>
       <c r="F2">
-        <v>0.291</v>
+        <v>0.0706</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1313.6</v>
+        <v>819.6</v>
       </c>
       <c r="L2">
-        <v>0.3469441656542179</v>
+        <v>0.2507035360332803</v>
       </c>
       <c r="M2">
-        <v>62.232</v>
+        <v>650.2230000000001</v>
       </c>
       <c r="N2">
-        <v>0.004383800956614233</v>
+        <v>0.08630285896312814</v>
       </c>
       <c r="O2">
-        <v>0.04737515225334957</v>
+        <v>0.7933418740849195</v>
       </c>
       <c r="P2">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="Q2">
-        <v>2.254171979233441e-06</v>
+        <v>3.052746144248892e-06</v>
       </c>
       <c r="R2">
-        <v>2.43605359317905e-05</v>
+        <v>2.806246949731576e-05</v>
       </c>
       <c r="S2">
-        <v>62.2</v>
+        <v>650.2</v>
       </c>
       <c r="T2">
-        <v>0.9994857950893432</v>
+        <v>0.999964627520097</v>
       </c>
       <c r="U2">
-        <v>4094.9</v>
+        <v>5910.9</v>
       </c>
       <c r="V2">
-        <v>0.2884565261800943</v>
+        <v>0.7845424862626423</v>
       </c>
       <c r="W2">
-        <v>0.1741528344911704</v>
+        <v>0.09416793051151248</v>
       </c>
       <c r="X2">
-        <v>0.0710226174208592</v>
+        <v>0.1213473976408315</v>
       </c>
       <c r="Y2">
-        <v>0.1031302170703112</v>
+        <v>-0.02717946712931901</v>
       </c>
       <c r="Z2">
-        <v>0.3983670549119872</v>
+        <v>0.2421575816833699</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05977544556254873</v>
+        <v>0.09665349155748168</v>
       </c>
       <c r="AC2">
-        <v>-0.05977544556254873</v>
+        <v>-0.09665349155748168</v>
       </c>
       <c r="AD2">
-        <v>9494.299999999999</v>
+        <v>8477.799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9494.299999999999</v>
+        <v>8477.799999999999</v>
       </c>
       <c r="AG2">
-        <v>5399.4</v>
+        <v>2566.9</v>
       </c>
       <c r="AH2">
-        <v>0.4007690943934623</v>
+        <v>0.529465400949288</v>
       </c>
       <c r="AI2">
-        <v>0.510588981865898</v>
+        <v>0.5140708850013643</v>
       </c>
       <c r="AJ2">
-        <v>0.2755456665629003</v>
+        <v>0.2541208383245389</v>
       </c>
       <c r="AK2">
-        <v>0.3723749818964269</v>
+        <v>0.2426043891650757</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="E3">
-        <v>0.15</v>
+        <v>0.081</v>
       </c>
       <c r="F3">
-        <v>0.291</v>
+        <v>0.0706</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1313.6</v>
+        <v>819.6</v>
       </c>
       <c r="L3">
-        <v>0.3469441656542179</v>
+        <v>0.2507035360332803</v>
       </c>
       <c r="M3">
-        <v>62.232</v>
+        <v>650.2230000000001</v>
       </c>
       <c r="N3">
-        <v>0.004383800956614233</v>
+        <v>0.08630285896312814</v>
       </c>
       <c r="O3">
-        <v>0.04737515225334957</v>
+        <v>0.7933418740849195</v>
       </c>
       <c r="P3">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="Q3">
-        <v>2.254171979233441e-06</v>
+        <v>3.052746144248892e-06</v>
       </c>
       <c r="R3">
-        <v>2.43605359317905e-05</v>
+        <v>2.806246949731576e-05</v>
       </c>
       <c r="S3">
-        <v>62.2</v>
+        <v>650.2</v>
       </c>
       <c r="T3">
-        <v>0.9994857950893432</v>
+        <v>0.999964627520097</v>
       </c>
       <c r="U3">
-        <v>4094.9</v>
+        <v>5910.9</v>
       </c>
       <c r="V3">
-        <v>0.2884565261800943</v>
+        <v>0.7845424862626423</v>
       </c>
       <c r="W3">
-        <v>0.1741528344911704</v>
+        <v>0.09416793051151248</v>
       </c>
       <c r="X3">
-        <v>0.0710226174208592</v>
+        <v>0.1213473976408315</v>
       </c>
       <c r="Y3">
-        <v>0.1031302170703112</v>
+        <v>-0.02717946712931901</v>
       </c>
       <c r="Z3">
-        <v>0.3983670549119872</v>
+        <v>0.2421575816833699</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05977544556254873</v>
+        <v>0.09665349155748168</v>
       </c>
       <c r="AC3">
-        <v>-0.05977544556254873</v>
+        <v>-0.09665349155748168</v>
       </c>
       <c r="AD3">
-        <v>9494.299999999999</v>
+        <v>8477.799999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9494.299999999999</v>
+        <v>8477.799999999999</v>
       </c>
       <c r="AG3">
-        <v>5399.4</v>
+        <v>2566.9</v>
       </c>
       <c r="AH3">
-        <v>0.4007690943934623</v>
+        <v>0.529465400949288</v>
       </c>
       <c r="AI3">
-        <v>0.510588981865898</v>
+        <v>0.5140708850013643</v>
       </c>
       <c r="AJ3">
-        <v>0.2755456665629003</v>
+        <v>0.2541208383245389</v>
       </c>
       <c r="AK3">
-        <v>0.3723749818964269</v>
+        <v>0.2426043891650757</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.128</v>
+        <v>0.336</v>
       </c>
       <c r="E2">
-        <v>0.081</v>
+        <v>0.404</v>
       </c>
       <c r="F2">
-        <v>0.0706</v>
+        <v>0.233</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>819.6</v>
+        <v>3139.5</v>
       </c>
       <c r="L2">
-        <v>0.2507035360332803</v>
+        <v>0.4033377013797888</v>
       </c>
       <c r="M2">
-        <v>650.2230000000001</v>
+        <v>424.5</v>
       </c>
       <c r="N2">
-        <v>0.08630285896312814</v>
+        <v>0.02104798643408931</v>
       </c>
       <c r="O2">
-        <v>0.7933418740849195</v>
+        <v>0.135212613473483</v>
       </c>
       <c r="P2">
-        <v>0.023</v>
+        <v>316.1</v>
       </c>
       <c r="Q2">
-        <v>3.052746144248892e-06</v>
+        <v>0.01567318848484248</v>
       </c>
       <c r="R2">
-        <v>2.806246949731576e-05</v>
+        <v>0.1006848224239529</v>
       </c>
       <c r="S2">
-        <v>650.2</v>
+        <v>108.4</v>
       </c>
       <c r="T2">
-        <v>0.999964627520097</v>
+        <v>0.255359246171967</v>
       </c>
       <c r="U2">
-        <v>5910.9</v>
+        <v>9959.5</v>
       </c>
       <c r="V2">
-        <v>0.7845424862626423</v>
+        <v>0.4938219573387808</v>
       </c>
       <c r="W2">
-        <v>0.09416793051151248</v>
+        <v>0.3201811050690282</v>
       </c>
       <c r="X2">
-        <v>0.1213473976408315</v>
+        <v>0.08727105392501175</v>
       </c>
       <c r="Y2">
-        <v>-0.02717946712931901</v>
+        <v>0.2329100511440164</v>
       </c>
       <c r="Z2">
-        <v>0.2421575816833699</v>
+        <v>0.3861050208831436</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09665349155748168</v>
+        <v>0.07822538822755104</v>
       </c>
       <c r="AC2">
-        <v>-0.09665349155748168</v>
+        <v>-0.07822538822755104</v>
       </c>
       <c r="AD2">
-        <v>8477.799999999999</v>
+        <v>17153.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8477.799999999999</v>
+        <v>17153.2</v>
       </c>
       <c r="AG2">
-        <v>2566.9</v>
+        <v>7193.700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.529465400949288</v>
+        <v>0.4596076245799997</v>
       </c>
       <c r="AI2">
-        <v>0.5140708850013643</v>
+        <v>0.5576299783166292</v>
       </c>
       <c r="AJ2">
-        <v>0.2541208383245389</v>
+        <v>0.2629093739835319</v>
       </c>
       <c r="AK2">
-        <v>0.2426043891650757</v>
+        <v>0.34582768467507</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,120 +704,239 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>MBH Bank Nyrt (BUSE:MBHBANK)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.481</v>
+      </c>
+      <c r="E3">
+        <v>0.5529999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>526.7</v>
+      </c>
+      <c r="L3">
+        <v>0.3066666666666667</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>3257.7</v>
+      </c>
+      <c r="V3">
+        <v>0.4396178292376827</v>
+      </c>
+      <c r="W3">
+        <v>0.3135865682305311</v>
+      </c>
+      <c r="X3">
+        <v>0.07559477963353704</v>
+      </c>
+      <c r="Y3">
+        <v>0.237991788596994</v>
+      </c>
+      <c r="Z3">
+        <v>0.1789584462134789</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.07378379090002665</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07378379090002665</v>
+      </c>
+      <c r="AD3">
+        <v>2164.3</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2164.3</v>
+      </c>
+      <c r="AG3">
+        <v>-1093.4</v>
+      </c>
+      <c r="AH3">
+        <v>0.226045996699601</v>
+      </c>
+      <c r="AI3">
+        <v>0.444697856952064</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.1730912314584685</v>
+      </c>
+      <c r="AK3">
+        <v>-0.6794680586626892</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>OTP Bank Nyrt. (BUSE:OTP)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.128</v>
-      </c>
-      <c r="E3">
-        <v>0.081</v>
-      </c>
-      <c r="F3">
-        <v>0.0706</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>819.6</v>
-      </c>
-      <c r="L3">
-        <v>0.2507035360332803</v>
-      </c>
-      <c r="M3">
-        <v>650.2230000000001</v>
-      </c>
-      <c r="N3">
-        <v>0.08630285896312814</v>
-      </c>
-      <c r="O3">
-        <v>0.7933418740849195</v>
-      </c>
-      <c r="P3">
-        <v>0.023</v>
-      </c>
-      <c r="Q3">
-        <v>3.052746144248892e-06</v>
-      </c>
-      <c r="R3">
-        <v>2.806246949731576e-05</v>
-      </c>
-      <c r="S3">
-        <v>650.2</v>
-      </c>
-      <c r="T3">
-        <v>0.999964627520097</v>
-      </c>
-      <c r="U3">
-        <v>5910.9</v>
-      </c>
-      <c r="V3">
-        <v>0.7845424862626423</v>
-      </c>
-      <c r="W3">
-        <v>0.09416793051151248</v>
-      </c>
-      <c r="X3">
-        <v>0.1213473976408315</v>
-      </c>
-      <c r="Y3">
-        <v>-0.02717946712931901</v>
-      </c>
-      <c r="Z3">
-        <v>0.2421575816833699</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.09665349155748168</v>
-      </c>
-      <c r="AC3">
-        <v>-0.09665349155748168</v>
-      </c>
-      <c r="AD3">
-        <v>8477.799999999999</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>8477.799999999999</v>
-      </c>
-      <c r="AG3">
-        <v>2566.9</v>
-      </c>
-      <c r="AH3">
-        <v>0.529465400949288</v>
-      </c>
-      <c r="AI3">
-        <v>0.5140708850013643</v>
-      </c>
-      <c r="AJ3">
-        <v>0.2541208383245389</v>
-      </c>
-      <c r="AK3">
-        <v>0.2426043891650757</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="D4">
+        <v>0.191</v>
+      </c>
+      <c r="E4">
+        <v>0.255</v>
+      </c>
+      <c r="F4">
+        <v>0.233</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2612.8</v>
+      </c>
+      <c r="L4">
+        <v>0.4307073504442576</v>
+      </c>
+      <c r="M4">
+        <v>424.5</v>
+      </c>
+      <c r="N4">
+        <v>0.03327350112479326</v>
+      </c>
+      <c r="O4">
+        <v>0.1624693815064299</v>
+      </c>
+      <c r="P4">
+        <v>316.1</v>
+      </c>
+      <c r="Q4">
+        <v>0.02477680496006396</v>
+      </c>
+      <c r="R4">
+        <v>0.1209813227189222</v>
+      </c>
+      <c r="S4">
+        <v>108.4</v>
+      </c>
+      <c r="T4">
+        <v>0.255359246171967</v>
+      </c>
+      <c r="U4">
+        <v>6701.8</v>
+      </c>
+      <c r="V4">
+        <v>0.5253058889002109</v>
+      </c>
+      <c r="W4">
+        <v>0.3267756419075253</v>
+      </c>
+      <c r="X4">
+        <v>0.09894732821648647</v>
+      </c>
+      <c r="Y4">
+        <v>0.2278283136910389</v>
+      </c>
+      <c r="Z4">
+        <v>0.5743188230170602</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.08266698555507543</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08266698555507543</v>
+      </c>
+      <c r="AD4">
+        <v>14988.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>14988.9</v>
+      </c>
+      <c r="AG4">
+        <v>8287.099999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.5402028342007006</v>
+      </c>
+      <c r="AI4">
+        <v>0.5788561056615432</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3937799952482774</v>
+      </c>
+      <c r="AK4">
+        <v>0.4317952084701077</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.336</v>
+        <v>0.159</v>
       </c>
       <c r="E2">
-        <v>0.404</v>
+        <v>0.198</v>
       </c>
       <c r="F2">
-        <v>0.233</v>
+        <v>0.0189</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3139.5</v>
+        <v>2682.5</v>
       </c>
       <c r="L2">
-        <v>0.4033377013797888</v>
+        <v>0.4383957900929906</v>
       </c>
       <c r="M2">
-        <v>424.5</v>
+        <v>517.3</v>
       </c>
       <c r="N2">
-        <v>0.02104798643408931</v>
+        <v>0.03442653498555855</v>
       </c>
       <c r="O2">
-        <v>0.135212613473483</v>
+        <v>0.1928424976700839</v>
       </c>
       <c r="P2">
-        <v>316.1</v>
+        <v>225</v>
       </c>
       <c r="Q2">
-        <v>0.01567318848484248</v>
+        <v>0.01497384568287391</v>
       </c>
       <c r="R2">
-        <v>0.1006848224239529</v>
+        <v>0.08387698042870456</v>
       </c>
       <c r="S2">
-        <v>108.4</v>
+        <v>292.3</v>
       </c>
       <c r="T2">
-        <v>0.255359246171967</v>
+        <v>0.5650492944132998</v>
       </c>
       <c r="U2">
-        <v>9959.5</v>
+        <v>10105.6</v>
       </c>
       <c r="V2">
-        <v>0.4938219573387808</v>
+        <v>0.6725319774793361</v>
       </c>
       <c r="W2">
-        <v>0.3201811050690282</v>
+        <v>0.2464740203059677</v>
       </c>
       <c r="X2">
-        <v>0.08727105392501175</v>
+        <v>0.0974783962517177</v>
       </c>
       <c r="Y2">
-        <v>0.2329100511440164</v>
+        <v>0.14899562405425</v>
       </c>
       <c r="Z2">
-        <v>0.3861050208831436</v>
+        <v>0.3222814465243176</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07822538822755104</v>
+        <v>0.08452900167225977</v>
       </c>
       <c r="AC2">
-        <v>-0.07822538822755104</v>
+        <v>-0.08452900167225977</v>
       </c>
       <c r="AD2">
-        <v>17153.2</v>
+        <v>15024.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17153.2</v>
+        <v>15024.7</v>
       </c>
       <c r="AG2">
-        <v>7193.700000000001</v>
+        <v>4919.1</v>
       </c>
       <c r="AH2">
-        <v>0.4596076245799997</v>
+        <v>0.4999750423448216</v>
       </c>
       <c r="AI2">
-        <v>0.5576299783166292</v>
+        <v>0.527267558974431</v>
       </c>
       <c r="AJ2">
-        <v>0.2629093739835319</v>
+        <v>0.2466295317693893</v>
       </c>
       <c r="AK2">
-        <v>0.34582768467507</v>
+        <v>0.267490674178077</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MBH Bank Nyrt (BUSE:MBHBANK)</t>
+          <t>OTP Bank Nyrt. (BUSE:OTP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.481</v>
+        <v>0.159</v>
       </c>
       <c r="E3">
-        <v>0.5529999999999999</v>
+        <v>0.198</v>
+      </c>
+      <c r="F3">
+        <v>0.0189</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,212 +734,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>526.7</v>
+        <v>2682.5</v>
       </c>
       <c r="L3">
-        <v>0.3066666666666667</v>
+        <v>0.4383957900929906</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>517.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03442653498555855</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1928424976700839</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>225</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01497384568287391</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.08387698042870456</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>292.3</v>
+      </c>
+      <c r="T3">
+        <v>0.5650492944132998</v>
       </c>
       <c r="U3">
-        <v>3257.7</v>
+        <v>10105.6</v>
       </c>
       <c r="V3">
-        <v>0.4396178292376827</v>
+        <v>0.6725319774793361</v>
       </c>
       <c r="W3">
-        <v>0.3135865682305311</v>
+        <v>0.2464740203059677</v>
       </c>
       <c r="X3">
-        <v>0.07559477963353704</v>
+        <v>0.0974783962517177</v>
       </c>
       <c r="Y3">
-        <v>0.237991788596994</v>
+        <v>0.14899562405425</v>
       </c>
       <c r="Z3">
-        <v>0.1789584462134789</v>
+        <v>0.3222814465243176</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07378379090002665</v>
+        <v>0.08452900167225977</v>
       </c>
       <c r="AC3">
-        <v>-0.07378379090002665</v>
+        <v>-0.08452900167225977</v>
       </c>
       <c r="AD3">
-        <v>2164.3</v>
+        <v>15024.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2164.3</v>
+        <v>15024.7</v>
       </c>
       <c r="AG3">
-        <v>-1093.4</v>
+        <v>4919.1</v>
       </c>
       <c r="AH3">
-        <v>0.226045996699601</v>
+        <v>0.4999750423448216</v>
       </c>
       <c r="AI3">
-        <v>0.444697856952064</v>
+        <v>0.527267558974431</v>
       </c>
       <c r="AJ3">
-        <v>-0.1730912314584685</v>
+        <v>0.2466295317693893</v>
       </c>
       <c r="AK3">
-        <v>-0.6794680586626892</v>
+        <v>0.267490674178077</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hungary</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OTP Bank Nyrt. (BUSE:OTP)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.191</v>
-      </c>
-      <c r="E4">
-        <v>0.255</v>
-      </c>
-      <c r="F4">
-        <v>0.233</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>2612.8</v>
-      </c>
-      <c r="L4">
-        <v>0.4307073504442576</v>
-      </c>
-      <c r="M4">
-        <v>424.5</v>
-      </c>
-      <c r="N4">
-        <v>0.03327350112479326</v>
-      </c>
-      <c r="O4">
-        <v>0.1624693815064299</v>
-      </c>
-      <c r="P4">
-        <v>316.1</v>
-      </c>
-      <c r="Q4">
-        <v>0.02477680496006396</v>
-      </c>
-      <c r="R4">
-        <v>0.1209813227189222</v>
-      </c>
-      <c r="S4">
-        <v>108.4</v>
-      </c>
-      <c r="T4">
-        <v>0.255359246171967</v>
-      </c>
-      <c r="U4">
-        <v>6701.8</v>
-      </c>
-      <c r="V4">
-        <v>0.5253058889002109</v>
-      </c>
-      <c r="W4">
-        <v>0.3267756419075253</v>
-      </c>
-      <c r="X4">
-        <v>0.09894732821648647</v>
-      </c>
-      <c r="Y4">
-        <v>0.2278283136910389</v>
-      </c>
-      <c r="Z4">
-        <v>0.5743188230170602</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.08266698555507543</v>
-      </c>
-      <c r="AC4">
-        <v>-0.08266698555507543</v>
-      </c>
-      <c r="AD4">
-        <v>14988.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>14988.9</v>
-      </c>
-      <c r="AG4">
-        <v>8287.099999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.5402028342007006</v>
-      </c>
-      <c r="AI4">
-        <v>0.5788561056615432</v>
-      </c>
-      <c r="AJ4">
-        <v>0.3937799952482774</v>
-      </c>
-      <c r="AK4">
-        <v>0.4317952084701077</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.159</v>
+        <v>0.3405</v>
       </c>
       <c r="E2">
-        <v>0.198</v>
+        <v>0.2945</v>
       </c>
       <c r="F2">
         <v>0.0189</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2682.5</v>
+        <v>3116.4</v>
       </c>
       <c r="L2">
-        <v>0.4383957900929906</v>
+        <v>0.3993285580656322</v>
       </c>
       <c r="M2">
         <v>517.3</v>
       </c>
       <c r="N2">
-        <v>0.03442653498555855</v>
+        <v>0.02440566335942328</v>
       </c>
       <c r="O2">
-        <v>0.1928424976700839</v>
+        <v>0.1659928122192273</v>
       </c>
       <c r="P2">
         <v>225</v>
       </c>
       <c r="Q2">
-        <v>0.01497384568287391</v>
+        <v>0.01061526049849263</v>
       </c>
       <c r="R2">
-        <v>0.08387698042870456</v>
+        <v>0.07219869079707354</v>
       </c>
       <c r="S2">
         <v>292.3</v>
@@ -639,55 +639,55 @@
         <v>0.5650492944132998</v>
       </c>
       <c r="U2">
-        <v>10105.6</v>
+        <v>12857.5</v>
       </c>
       <c r="V2">
-        <v>0.6725319774793361</v>
+        <v>0.6066031638194178</v>
       </c>
       <c r="W2">
-        <v>0.2464740203059677</v>
+        <v>0.2069045766782442</v>
       </c>
       <c r="X2">
-        <v>0.0974783962517177</v>
+        <v>0.0925131483499054</v>
       </c>
       <c r="Y2">
-        <v>0.14899562405425</v>
+        <v>0.1143914283283388</v>
       </c>
       <c r="Z2">
-        <v>0.3222814465243176</v>
+        <v>0.3809516836052289</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08452900167225977</v>
+        <v>0.08577559087373961</v>
       </c>
       <c r="AC2">
-        <v>-0.08452900167225977</v>
+        <v>-0.08577559087373961</v>
       </c>
       <c r="AD2">
-        <v>15024.7</v>
+        <v>18710.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15024.7</v>
+        <v>18710.8</v>
       </c>
       <c r="AG2">
-        <v>4919.1</v>
+        <v>5853.299999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4999750423448216</v>
+        <v>0.4688636244039222</v>
       </c>
       <c r="AI2">
-        <v>0.527267558974431</v>
+        <v>0.5272786707847691</v>
       </c>
       <c r="AJ2">
-        <v>0.2466295317693893</v>
+        <v>0.2163945698948582</v>
       </c>
       <c r="AK2">
-        <v>0.267490674178077</v>
+        <v>0.2586739496466782</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0.2464740203059677</v>
       </c>
       <c r="X3">
-        <v>0.0974783962517177</v>
+        <v>0.09746673287261977</v>
       </c>
       <c r="Y3">
-        <v>0.14899562405425</v>
+        <v>0.149007287433348</v>
       </c>
       <c r="Z3">
         <v>0.3222814465243176</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08452900167225977</v>
+        <v>0.08452316969162021</v>
       </c>
       <c r="AC3">
-        <v>-0.08452900167225977</v>
+        <v>-0.08452316969162021</v>
       </c>
       <c r="AD3">
         <v>15024.7</v>
@@ -818,6 +818,125 @@
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MBH Bank Nyrt (BUSE:MBHBANK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.522</v>
+      </c>
+      <c r="E4">
+        <v>0.391</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>433.9</v>
+      </c>
+      <c r="L4">
+        <v>0.257476857346309</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2751.9</v>
+      </c>
+      <c r="V4">
+        <v>0.4460346532246301</v>
+      </c>
+      <c r="W4">
+        <v>0.1673351330505206</v>
+      </c>
+      <c r="X4">
+        <v>0.08755956382719104</v>
+      </c>
+      <c r="Y4">
+        <v>0.07977556922332957</v>
+      </c>
+      <c r="Z4">
+        <v>1.12376633769005</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.087028012055859</v>
+      </c>
+      <c r="AC4">
+        <v>-0.087028012055859</v>
+      </c>
+      <c r="AD4">
+        <v>3686.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>3686.1</v>
+      </c>
+      <c r="AG4">
+        <v>934.1999999999998</v>
+      </c>
+      <c r="AH4">
+        <v>0.3740031250634144</v>
+      </c>
+      <c r="AI4">
+        <v>0.5273239678406912</v>
+      </c>
+      <c r="AJ4">
+        <v>0.131505229521812</v>
+      </c>
+      <c r="AK4">
+        <v>0.2204185640469056</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
